--- a/results/tables/penalty_sensitivity_smoke/speedup_penalty_multi_seed.xlsx
+++ b/results/tables/penalty_sensitivity_smoke/speedup_penalty_multi_seed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="speedup_penalty_multi_seed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="speedup_penalty_multi_seed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01330969999253284</v>
+        <v>0.022368099889718</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -867,7 +867,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01147730000957381</v>
+        <v>0.009146400028839707</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01032039998972323</v>
+        <v>0.03095719998236746</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1187,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009813199998461641</v>
+        <v>0.01670599996577948</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09781269999803044</v>
+        <v>0.01406089996453375</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01023240000358783</v>
+        <v>0.02274309995118529</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1667,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009713299994473346</v>
+        <v>0.01513129996601492</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0116373999917414</v>
+        <v>0.02764019998721778</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0240334999980405</v>
+        <v>0.01911799993831664</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01188259999617003</v>
+        <v>0.01687729998957366</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0113462999870535</v>
+        <v>0.02204640000127256</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01363680000940803</v>
+        <v>0.02015999995637685</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01213509999797679</v>
+        <v>0.01898940000683069</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01166469999589026</v>
+        <v>0.02057179994881153</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01396589999785647</v>
+        <v>0.01686550001613796</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -3107,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01447470000130124</v>
+        <v>0.02319790003821254</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.009959599992725998</v>
+        <v>0.02364280004985631</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01054460000887047</v>
+        <v>0.03025860001798719</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01046000000496861</v>
+        <v>0.02926049998495728</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01154149998910725</v>
+        <v>0.02700139989610761</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0.01156089999130927</v>
+        <v>0.02766010002233088</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01091499999165535</v>
+        <v>0.02458760002627969</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01071909999882337</v>
+        <v>0.03139159991405904</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0.01046600000699982</v>
+        <v>0.08090959989931434</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.01058919999923091</v>
+        <v>0.03707449999637902</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -4707,7 +4707,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.01355810000677593</v>
+        <v>0.05619839997962117</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.01144440000643954</v>
+        <v>0.03169470001012087</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01095009999698959</v>
+        <v>0.01723260001745075</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -5187,7 +5187,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.01077599999553058</v>
+        <v>0.04573000001255423</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -5347,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0.009755499995662831</v>
+        <v>0.02554319996852428</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -5507,7 +5507,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.009614399998099543</v>
+        <v>0.02836160000879318</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0.009210600008373149</v>
+        <v>0.01773960003629327</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
